--- a/Carta_Gantt_Organizate_COMPLETO.xlsx
+++ b/Carta_Gantt_Organizate_COMPLETO.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4DC17F-83B1-42C2-AED0-7A36F4358D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen del Proyecto" sheetId="1" r:id="rId1"/>
